--- a/forms/trg/Formulir_TRG_amrg.xlsx
+++ b/forms/trg/Formulir_TRG_amrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B44)</f>
+        <f>COUNTA(Anggota!B5:B45)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F44)</f>
+        <f>COUNTA(Anggota!F5:F45)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Nurmujahidin, S.P., M.Si.</t>
+          <t>Prof. Dr. Tutik Kuswinanti, M.Sc.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Bacteriology</t>
+          <t>Phytopathology, Biological Control, Biotechnology, Mycology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-1076-6818</t>
+          <t>0009-0005-1202-3853</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6915260</t>
+          <t>6015408</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>58651425300</t>
+          <t>55792741300</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Eirene Brugman, S.P., M.Sc.</t>
+          <t>Nurmujahidin, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Bacteriology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6935-6385</t>
+          <t>0009-0007-1076-6818</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6857698</t>
+          <t>6915260</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57475371400</t>
+          <t>58651425300</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1007,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mustika Tuwo, S.Si., M.Si.</t>
+          <t>Eirene Brugman, S.P., M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Department of Biology, Faculty of Mathematics and Natural Sciences, Hasanuddin University</t>
+          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Plant Tissue Culture</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,17 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8721-2780</t>
+          <t>0000-0002-6935-6385</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6749621</t>
+          <t>6857698</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57210063480</t>
+          <t>57475371400</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1060,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. Masniawati., S.Si., M.Si.</t>
+          <t>Dr. Mustika Tuwo, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1075,22 +1071,26 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Biologi, Biotechnology</t>
+          <t>Plant Tissue Culture</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8721-2780</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6018522</t>
+          <t>6749621</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57201353232</t>
+          <t>57210063480</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1105,41 +1105,37 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
+          <t>Dr. A. Masniawati., S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
+          <t>Department of Biology, Faculty of Mathematics and Natural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Sciences, Plant Pathology, Plant Pest Science, Microbiology, Biological Control of Plant Diseases</t>
+          <t>Biologi, Biotechnology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7116-5887</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6038586</t>
+          <t>6018522</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>54795337200</t>
+          <t>57201353232</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1154,12 +1150,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Itji Diana Daud., M.S.</t>
+          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Biological Control and Conservation of Natural Enemies</t>
+          <t>Agricultural Sciences, Plant Pathology, Plant Pest Science, Microbiology, Biological Control of Plant Diseases</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1178,17 +1174,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-8066-6819</t>
+          <t>0000-0002-7116-5887</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6027235</t>
+          <t>6038586</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57191167146</t>
+          <t>54795337200</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1203,12 +1199,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nurmujahidin, S.P., M.Si.</t>
+          <t>Prof. Dr. Itji Diana Daud., M.S.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1218,7 +1214,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Bacteriology</t>
+          <t>Biological Control and Conservation of Natural Enemies</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1227,17 +1223,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-1076-6818</t>
+          <t>0009-0001-8066-6819</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6915260</t>
+          <t>6027235</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>58651425300</t>
+          <t>57191167146</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1252,12 +1248,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Eirene Brugman, S.P., M.Sc.</t>
+          <t>Nurmujahidin, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1267,7 +1263,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Bacteriology</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1276,17 +1272,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6935-6385</t>
+          <t>0009-0007-1076-6818</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>6857698</t>
+          <t>6915260</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57475371400</t>
+          <t>58651425300</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1301,22 +1297,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mustika Tuwo, S.Si., M.Si.</t>
+          <t>Eirene Brugman, S.P., M.Sc.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Department of Biology, Faculty of Mathematics and Natural Sciences, Hasanuddin University</t>
+          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Plant Tissue Culture</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1325,17 +1321,17 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8721-2780</t>
+          <t>0000-0002-6935-6385</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6749621</t>
+          <t>6857698</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57210063480</t>
+          <t>57475371400</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1350,12 +1346,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. Masniawati., S.Si., M.Si.</t>
+          <t>Dr. Mustika Tuwo, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1365,22 +1361,26 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Biologi, Biotechnology</t>
+          <t>Plant Tissue Culture</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-8721-2780</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>6018522</t>
+          <t>6749621</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57201353232</t>
+          <t>57210063480</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1395,41 +1395,37 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
+          <t>Dr. A. Masniawati., S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
+          <t>Department of Biology, Faculty of Mathematics and Natural Sciences, Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Sciences, Plant Pathology, Plant Pest Science, Microbiology, Biological Control of Plant Diseases</t>
+          <t>Biologi, Biotechnology</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7116-5887</t>
-        </is>
-      </c>
+      <c r="J15" s="12" t="n"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>6038586</t>
+          <t>6018522</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>54795337200</t>
+          <t>57201353232</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1444,12 +1440,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Itji Diana Daud., M.S.</t>
+          <t>Muhammad Junaid, S.P., M.P., Ph.D.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Biological Control and Conservation of Natural Enemies</t>
+          <t>Agricultural Sciences, Plant Pathology, Plant Pest Science, Microbiology, Biological Control of Plant Diseases</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1468,17 +1464,17 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-8066-6819</t>
+          <t>0000-0002-7116-5887</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
         <is>
-          <t>6027235</t>
+          <t>6038586</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>57191167146</t>
+          <t>54795337200</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1493,12 +1489,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Baharuddin, Dipl. Ing. Agr.</t>
+          <t>Prof. Dr. Itji Diana Daud., M.S.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1508,7 +1504,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Bacteriology</t>
+          <t>Biological Control and Conservation of Natural Enemies</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1517,17 +1513,17 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5109-8090</t>
+          <t>0009-0001-8066-6819</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
         <is>
-          <t>6016070</t>
+          <t>6027235</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>57202610804</t>
+          <t>57191167146</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1542,33 +1538,41 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Didier Lesueur, Ph.D.</t>
+          <t>Prof. Dr. Baharuddin, Dipl. Ing. Agr.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>CIRAD, UMR Eco&amp;Sol, Montpellier, France</t>
+          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Plant Science, Agronomy, Soil Science</t>
+          <t>Bacteriology</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5109-8090</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>6016070</t>
+        </is>
+      </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>56249008500</t>
+          <t>57202610804</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -1583,37 +1587,33 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eriyanto Yusnawan</t>
+          <t>Didier Lesueur, Ph.D.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>CIRAD, UMR Eco&amp;Sol, Montpellier, France</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology, Plant protection, Plant science</t>
+          <t>Agricultural Plant Science, Agronomy, Soil Science</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-8641-8445</t>
-        </is>
-      </c>
+      <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>55416508900</t>
+          <t>56249008500</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muh. Akhsan Akib, M.S.</t>
+          <t>Dr. Eriyanto Yusnawan</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Muhammadiyah Parepare University</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Plant Physiology, Mycorrhiza, Ecology</t>
+          <t>Phytopathology, Plant protection, Plant science</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1652,17 +1652,13 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>%200000-0001-6777-7891</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>6061465</t>
-        </is>
-      </c>
+          <t>0000-0002-8641-8445</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="n"/>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>57221719448</t>
+          <t>55416508900</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -1677,22 +1673,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Hishar Mirsam, S.P., M.Si.</t>
+          <t>Dr. Muh. Akhsan Akib, M.S.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>Muhammadiyah Parepare University</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Plant Protection, Mycology</t>
+          <t>Plant Physiology, Mycorrhiza, Ecology</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1701,17 +1697,17 @@
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7450-8574</t>
+          <t>%200000-0001-6777-7891</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>6734476</t>
+          <t>6061465</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>57217086730</t>
+          <t>57221719448</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -1726,12 +1722,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Erwin Najamuddin, S.P., M.Si.</t>
+          <t>Hishar Mirsam, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1741,7 +1737,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Plant Protection, Mycology</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1750,17 +1746,17 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3991-1955</t>
+          <t>0000-0002-7450-8574</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>6672957</t>
+          <t>6734476</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>57226563959</t>
+          <t>57217086730</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -1775,17 +1771,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Hikmawati</t>
+          <t>Erwin Najamuddin, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Al Asyariah Mandar University</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1797,13 +1793,21 @@
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3991-1955</t>
+        </is>
+      </c>
       <c r="K23" s="11" t="inlineStr">
         <is>
-          <t>6701522</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="n"/>
+          <t>6672957</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>57226563959</t>
+        </is>
+      </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1816,22 +1820,22 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Ramdani</t>
+          <t>Hikmawati</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
+          <t>Al Asyariah Mandar University</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Plant Protection, Mycology</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1839,7 +1843,11 @@
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>6701522</t>
+        </is>
+      </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="11" t="inlineStr">
         <is>
@@ -1853,22 +1861,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Syatrawati</t>
+          <t>Ramdani</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>State Polytechnic of Agriculture of Pangkajene Kepulauan</t>
+          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Plant Protection, Mycology</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1876,16 +1884,8 @@
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="12" t="n"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>6038539</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>59637970800</t>
-        </is>
-      </c>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1898,22 +1898,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Gaby Maulida Nurdin</t>
+          <t>Syatrawati</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>West Sulawesi University</t>
+          <t>State Polytechnic of Agriculture of Pangkajene Kepulauan</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Microbiology, Molecular Biology</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1923,12 +1923,12 @@
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
-          <t>6644252</t>
+          <t>6038539</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>59019656700</t>
+          <t>59637970800</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -1943,41 +1943,37 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Ernawati Djaya</t>
+          <t>Gaby Maulida Nurdin</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>West Sulawesi University</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Mycology</t>
+          <t>Microbiology, Molecular Biology</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2465-4733</t>
-        </is>
-      </c>
+      <c r="J27" s="12" t="n"/>
       <c r="K27" s="11" t="inlineStr">
         <is>
-          <t>6673129</t>
+          <t>6644252</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>58195948400</t>
+          <t>59019656700</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Nurasiah Djaenuddin</t>
+          <t>Ernawati Djaya</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -2016,17 +2012,17 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4167-1436</t>
+          <t>0000-0002-2465-4733</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
-          <t>6674057</t>
+          <t>6673129</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>57217525713</t>
+          <t>58195948400</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2041,31 +2037,43 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Kurniawan</t>
+          <t>Nurasiah Djaenuddin</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Plant Science, Agronomy</t>
+          <t>Mycology</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4167-1436</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>6674057</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>57217525713</t>
+        </is>
+      </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -2078,22 +2086,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Fitrianti</t>
+          <t>Kurniawan</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Al Asyariah Mandar University</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Plant Protection, Mycology</t>
+          <t>Agricultural Plant Science, Agronomy</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -2101,11 +2109,7 @@
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>6667168</t>
-        </is>
-      </c>
+      <c r="K30" s="12" t="n"/>
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="11" t="inlineStr">
         <is>
@@ -2119,22 +2123,22 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Yenni Yendri Salosa</t>
+          <t>Fitrianti</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Papua University, West Papua, Indonesia</t>
+          <t>Al Asyariah Mandar University</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Plant Protection, Mycology</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -2144,14 +2148,10 @@
       <c r="J31" s="12" t="n"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>6673227</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>58564548500</t>
-        </is>
-      </c>
+          <t>6667168</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="n"/>
       <c r="M31" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -2164,41 +2164,37 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Baharuddin, Dipl. Ing. Agr.</t>
+          <t>Yenni Yendri Salosa</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
+          <t>Papua University, West Papua, Indonesia</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Bacteriology</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5109-8090</t>
-        </is>
-      </c>
+      <c r="J32" s="12" t="n"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>6016070</t>
+          <t>6673227</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>57202610804</t>
+          <t>58564548500</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr">
@@ -2211,18 +2207,50 @@
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Baharuddin, Dipl. Ing. Agr.</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Department of Plant Pests and Disease, Hasanuddin University, Makassar, Indonesia</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Bacteriology</t>
+        </is>
+      </c>
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5109-8090</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>6016070</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>57202610804</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2411,15 +2439,32 @@
       <c r="L44" s="12" t="n"/>
       <c r="M44" s="12" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="12" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="12" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
